--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>صورة الهيرو الكبيرة (كمبيوتر) — عرض الصفحة كله. مقاس مقترح 1600×700</t>
+          <t>صورة الهيرو الكبيرة (كمبيوتر) — عرض الصفحة كله. مقاس مقترح 1600×800</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>#2B463C</t>
+          <t>#5A3114</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>#2B463C</t>
+          <t>#5A3114</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>#2B463C</t>
+          <t>#5A3114</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>الفوتر والشريط المتحرك وأزرار الإضافة للسلة</t>
+          <t>الفوتر والشريط السفلي وهيدر السلة (بني الهوية)</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>#2B463C</t>
+          <t>#5A3114</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>زر السلة والشارة وأيقونات الثقة</t>
+          <t>الفوتر والشريط السفلي وهيدر السلة (بني الهوية)</t>
         </is>
       </c>
     </row>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>صورة الهيرو الكبيرة (كمبيوتر) — عرض الصفحة كله. مقاس مقترح 1600×800</t>
+          <t>صورة الهيرو الكبيرة (كمبيوتر) — عرض الصفحة كله. مقاس مقترح 1600×900</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>نعم / لا — مربعات الأقسام الملونة اللي تحت السلايدر في الصفحة الرئيسية</t>
+          <t>نعم / لا — مربعات الأقسام تحت الصورة الكبيرة في الصفحة الرئيسية (دلوقتي: لا)</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2080,156 +2080,224 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>إظهار وصف صفحة حول القديم</t>
+          <t>إظهار خطوات الطلب</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>النصين القديمين تحت اسم المتجر (وصف صفحة حول 1 والمساحة الحرة). نعم/لا</t>
+          <t>نعم / لا — الخطوات الثلاثة (1 2 3) اللي في صفحة حول</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>كروت صفحة حول (قناة العروض / الموقع / التواصل)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>خطوة 1</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>اختار منتجاتك</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>سيبها فاضية لو مش عايزها</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>عنوان كيو آر قناة العروض</t>
+          <t>خطوة 2</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>قناة العروض (واتساب)</t>
+          <t>راجع السلة</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>عنوان الكارت</t>
+          <t>سيبها فاضية لو مش عايزها</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>رابط قناة العروض</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n"/>
+          <t>خطوة 3</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>ابعت الطلب واتساب</t>
+        </is>
+      </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>رابط قناة واتساب الخاصة بالمتجر. فاضي = الكارت يختفي من صفحة حول</t>
+          <t>سيبها فاضية لو مش عايزها</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>نص زر قناة العروض</t>
+          <t>إظهار وصف صفحة حول القديم</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>الانتقال إلى القناة</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>كتابة الزر</t>
+          <t>النصين القديمين تحت اسم المتجر (وصف صفحة حول 1 والمساحة الحرة). نعم/لا</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>عنوان كيو آر الموقع</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>موقعنا الإلكتروني</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>عنوان الكارت</t>
-        </is>
-      </c>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>كروت صفحة حول (قناة العروض / الموقع / التواصل)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>رابط الموقع</t>
+          <t>عنوان كيو آر قناة العروض</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>https://truly.market.page</t>
+          <t>قناة العروض (واتساب)</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>الرابط اللي بيتشارك</t>
+          <t>عنوان الكارت</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>نص زر الموقع</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>مشاركة الموقع</t>
-        </is>
-      </c>
+          <t>رابط قناة العروض</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>كتابة الزر</t>
+          <t>رابط قناة واتساب الخاصة بالمتجر. فاضي = الكارت يختفي من صفحة حول</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>عنوان كيو آر التواصل</t>
+          <t>نص زر قناة العروض</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>تواصل معنا</t>
+          <t>الانتقال إلى القناة</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>عنوان الكارت</t>
+          <t>كتابة الزر</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
+          <t>عنوان كيو آر الموقع</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>موقعنا الإلكتروني</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>عنوان الكارت</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>رابط الموقع</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>https://truly.market.page</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>الرابط اللي بيتشارك</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>نص زر الموقع</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>مشاركة الموقع</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>كتابة الزر</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>عنوان كيو آر التواصل</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>تواصل معنا</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>عنوان الكارت</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
           <t>نص زر التواصل</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>مراسلة للإستفسار</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>كتابة الزر</t>
         </is>
@@ -2397,7 +2465,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>seedling</t>
+          <t>bowl-food</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -2432,7 +2500,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>cookie</t>
+          <t>cookie-bite</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -2502,7 +2570,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>cart-shopping</t>
+          <t>basket-shopping</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -2572,7 +2640,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>bread-slice</t>
+          <t>wheat-awn</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -2642,7 +2710,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>cake-candles</t>
+          <t>ice-cream</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -4517,12 +4585,12 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>الدفع عند الاستلام,فودافون كاش,إنستا باي</t>
+          <t>الدفع عند الاستلام,إنستا باي</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>اكتبهم بينهم فاصلة. بتظهر كقائمة اختيار في السلة</t>
+          <t>اكتب اللي تحبه بينهم فاصلة (مثال: الدفع عند الاستلام,إنستا باي,فودافون كاش). بتظهر كقائمة اختيار في السلة</t>
         </is>
       </c>
     </row>
@@ -4551,12 +4619,12 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>طلب جديد من</t>
+          <t>فاتورة</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>أول سطر في رسالة الواتساب</t>
+          <t>(غير مستخدم حالياً — أول سطر في الرسالة «فاتورة» ثابت)</t>
         </is>
       </c>
     </row>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1233,115 +1233,98 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>إظهار أقسام الصفحة الرئيسية</t>
+          <t>شكل شريط التنقل السفلي</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>ملتصق</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>نعم / لا — مربعات الأقسام تحت الصورة الكبيرة في الصفحة الرئيسية (دلوقتي: لا)</t>
+          <t>ملتصق (لازق في آخر الشاشة) / كبسولة (عايم ومدوّر) — في الموبايل بس</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>شكل شريط التنقل السفلي</t>
+          <t>إظهار البنر السفلي</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>ملتصق</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>ملتصق (لازق في آخر الشاشة) / كبسولة (عايم ومدوّر) — في الموبايل بس</t>
+          <t>نعم / لا — بنر «اطلب دلوقتي على واتساب» اللي في آخر البنرات</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>إظهار البنر السفلي</t>
+          <t>تشغيل السلايدر تلقائياً</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>نعم / لا — بنر «اطلب دلوقتي على واتساب» اللي في آخر البنرات</t>
+          <t>نعم / لا</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>تشغيل السلايدر تلقائياً</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
+          <t>مدة الانتقال بالثواني</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>نعم / لا</t>
+          <t>كل كام ثانية يتحرك السلايدر</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>مدة الانتقال بالثواني</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>3</v>
+          <t>إظهار اسم القسم على السلايدر</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>كل كام ثانية يتحرك السلايدر</t>
+          <t>نعم / لا</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>إظهار اسم القسم على السلايدر</t>
+          <t>تحريك الأقسام السريعة</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>نعم / لا</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>تحريك الأقسام السريعة</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>نعم = تلف لوحدها، لا = سحب عادي</t>
         </is>
@@ -3006,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3199,6 +3182,231 @@
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>تسوّق المخبوزات</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>images/banner-slider-4.svg</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>مشروبات منعشة</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>قسم</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>المشروبات</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>مشروبات منعشة</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>عصاير وغازيات ومياه بأحسن سعر</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>تسوّق المشروبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>images/banner-slider-5.svg</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>تسالي اللمّة</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>قسم</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>التسالي</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>تسالي لكل لمّة</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>شيبسي وشوكولاتة وبسكويت</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>تسوّق التسالي</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>images/banner-slider-6.svg</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>مكسرات طازجة</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>قسم</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>مكسرات</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>مكسرات طازجة</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>لوز وكاجو وفستق ولب</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>تسوّق المكسرات</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>images/banner-slider-7.svg</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>البقالة</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>قسم</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>البقالة</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>كل احتياجات المطبخ</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>أرز ومكرونة وزيت وبقوليات</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>تسوّق البقالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>images/banner-slider-8.svg</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>اطلب دلوقتي</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>قسم</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>عروض اليوم</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>اطلب وإحنا نوصّل</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>توصيل سريع لحد باب البيت</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>شوف العروض</t>
         </is>
       </c>
     </row>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -55,7 +55,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3EBDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A3114"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,6 +142,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -567,12 +575,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الشيت</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>الشرح</t>
         </is>
@@ -683,6 +691,30 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>قبل أي تعديل كبير احفظ نسخة من الملفين على جهازك.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>طرق الدفع</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>شيت «الطلب والدفع» ← صف «طرق الدفع». اكتب أي طرق بينها فاصلة (مثال: الدفع عند الاستلام,إنستا باي,فودافون كاش). بتظهر للزبون كقائمة اختيار، وتقدر تضيف أو تشيل براحتك.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>صور المنتجات الكتير</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>لو هترفع مئات الصور: اضغطها قبل الرفع (مقاس 600×600، صيغة WebP أو JPG، أقل من 60 كيلوبايت للصورة) وسمّيها بأسماء إنجليزي صغيرة من غير مسافات (مثال: chipsy-cheese.webp). الموقع بيحمّل الصور ساعة ما الزبون يوصل لها بس، ومبيحمّلش الكل مرة واحدة.</t>
         </is>
       </c>
     </row>
@@ -698,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -707,17 +739,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -752,122 +784,118 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>إظهار شارة الهيرو</t>
+          <t>صورة الهيرو</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>images/hero.svg</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>الشارة الخضرا اللي فيها اسم المتجر فوق عنوان الهيرو (نعم/لا)</t>
+          <t>صورة الهيرو الكبيرة (كمبيوتر) — عرض الصفحة كله. مقاس مقترح 1600×900</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>نص شارة الهيرو</t>
+          <t>صورة الهيرو (موبايل)</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>ترولي ماركت</t>
+          <t>images/hero-mobile.svg</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>الكبسولة الخضرا فوق عنوان الصفحة الرئيسية (الفاضي = اسم المتجر). تتقفل من «إظهار شارة الهيرو»</t>
+          <t>نسخة الموبايل من الصورة. مقاس مقترح 800×1000 (فاضي = نفس صورة الكمبيوتر)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>نص الكبسولة الخفيفة</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n"/>
+          <t>رابط الهيرو</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>#categories</t>
+        </is>
+      </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>كلمة صغيرة في كبسولة تحت شارة الهيرو (فاضي = مخفية)</t>
+          <t>لما العميل يضغط على الصورة يروح فين</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>لون شارة الهيرو</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>#FF6200</t>
+          <t>إظهار الشريط المتحرك</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>الشارة الخضرا اللي فيها اسم المتجر والعربية</t>
+          <t>الشريط تحت الهيرو (نعم/لا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>سطر الهيرو 1</t>
+          <t>نص الشريط المتحرك</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>كل طلبات البيت</t>
+          <t>توصيل سريع لحد البيت  •  أسعار واضحة  •  اطلب من واتساب في ثواني</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>السطر الأول (بلون النص العادي)</t>
+          <t>اكتب اللي تحبه، افصل بين الجمل بـ •</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>سطر الهيرو 2</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>لحد البيت</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>السطر التاني (بيظهر بالألوان اللي تحت)</t>
-        </is>
-      </c>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>السلايدر والبنرات والتنقل</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>لون السطر الملوّن في الهيرو</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>#FF6200</t>
+          <t>شكل شريط التنقل السفلي</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>ملتصق</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>لون السطر التاني (كود مثل #FF6200)</t>
+          <t>ملتصق (لازق في آخر الشاشة) / كبسولة (عايم ومدوّر) — في الموبايل بس</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>إظهار وصف الهيرو</t>
+          <t>إظهار البنر السفلي</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -877,459 +905,98 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>نعم = يظهر وصف الموقع بخط صغير تحت الجملة</t>
+          <t>نعم / لا — بنر «اطلب دلوقتي على واتساب» اللي في آخر البنرات</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>زر الهيرو 1 (نص)</t>
+          <t>تشغيل السلايدر تلقائياً</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>تسوّق الآن</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>نص الزرار البرتقالي</t>
+          <t>نعم / لا</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>زر الهيرو 1 (رابط)</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>#categories</t>
-        </is>
+          <t>مدة الانتقال بالثواني</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>#categories أو #catalog أو #categories/اسم القسم</t>
+          <t>كل كام ثانية يتحرك السلايدر</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>لون زر الهيرو 1</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>#FF6200</t>
+          <t>إظهار اسم القسم على السلايدر</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>زرار "تسوّق الآن" (بيظهر بخلفية خفيفة بنفس اللون)</t>
+          <t>نعم / لا</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>زر الهيرو 2 (نص)</t>
+          <t>تحريك الأقسام السريعة</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>عروض اليوم</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>نص الزرار التاني</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>زر الهيرو 2 (رابط)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>#catalog</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>نفس صيغة الرابط فوق</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>لون زر الهيرو 2</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>#5C9A47</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>زرار "عروض اليوم"</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>نقطة ثقة 1</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>bolt|توصيل سريع</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>العمود الأول (فوق زر «تسوّق الآن»، أخضر) — الشكل: اسم أيقونة|النص</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>نقطة ثقة 2</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>tags|أسعار واضحة</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>العمود الأول — سيبها فاضية لو مش عايزها</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>نقطة ثقة 3</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>whatsapp|اطلب من واتساب</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>العمود الأول — سيبها فاضية لو مش عايزها</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>نقطة ثقة 4</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>star|جودة مضمونة</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>العمود الثاني (فوق زر «عروض اليوم»، برتقالي) — الشكل: اسم أيقونة|النص</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>نقطة ثقة 5</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>rotate-left|استبدال سهل</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>العمود الثاني — سيبها فاضية لو مش عايزها</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>نقطة ثقة 6</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>headset|خدمة عملاء</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>العمود الثاني — سيبها فاضية لو مش عايزها</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>لون نقاط الثقة (فوق الزر الأول)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>#5C9A47</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>لون العمود الأول من نقاط الثقة (أخضر)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>لون نقاط الثقة (فوق الزر الثاني)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>#FF6200</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>لون العمود الثاني من نقاط الثقة (برتقالي)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>إظهار نقطة التوصيل المجاني في الهيرو</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>نعم / لا — سطر «توصيل مجاني فوق ...» وسط نقاط الثقة في الهيرو</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>صورة الهيرو</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>images/hero.svg</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>صورة الهيرو الكبيرة (كمبيوتر) — عرض الصفحة كله. مقاس مقترح 1600×900</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>صورة الهيرو (موبايل)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>images/hero-mobile.svg</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>نسخة الموبايل من الصورة. مقاس مقترح 800×1000 (فاضي = نفس صورة الكمبيوتر)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>رابط الهيرو</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>#categories</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>لما العميل يضغط على الصورة يروح فين</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>إظهار الشريط المتحرك</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>الشريط تحت الهيرو (نعم/لا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>نص الشريط المتحرك</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>توصيل سريع لحد البيت  •  أسعار واضحة  •  اطلب من واتساب في ثواني</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>اكتب اللي تحبه، افصل بين الجمل بـ •</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>السلايدر والبنرات والتنقل</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>شكل شريط التنقل السفلي</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>ملتصق</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>ملتصق (لازق في آخر الشاشة) / كبسولة (عايم ومدوّر) — في الموبايل بس</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>إظهار البنر السفلي</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>نعم / لا — بنر «اطلب دلوقتي على واتساب» اللي في آخر البنرات</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>تشغيل السلايدر تلقائياً</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>نعم / لا</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>مدة الانتقال بالثواني</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>كل كام ثانية يتحرك السلايدر</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>إظهار اسم القسم على السلايدر</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>نعم / لا</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>تحريك الأقسام السريعة</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
           <t>نعم = تلف لوحدها، لا = سحب عادي</t>
         </is>
       </c>
     </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1"/>
   </sheetData>
   <dataValidations count="11">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="اختار من القائمة" type="list" errorStyle="warning">
@@ -1386,17 +1053,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -1532,7 +1199,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003B86C9"/>
+    <tabColor rgb="00F9B914"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1545,17 +1212,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -1807,11 +1474,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007C5CBF"/>
+    <tabColor rgb="00DE5718"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1820,17 +1487,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -2063,63 +1730,63 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>إظهار خطوات الطلب</t>
+          <t>إحصائية 3 (رقم)</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>24/7</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>نعم / لا — الخطوات الثلاثة (1 2 3) اللي في صفحة حول</t>
+          <t>الرقم الكبير في الخانة التالتة تحت اسم المتجر (الأولى والتانية بتتحسب لوحدها: عدد المنتجات والأقسام)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>خطوة 1</t>
+          <t>إحصائية 3 (نص)</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>اختار منتجاتك</t>
+          <t>اطلب في أي وقت</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>سيبها فاضية لو مش عايزها</t>
+          <t>الكلام تحت الرقم</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>خطوة 2</t>
+          <t>إظهار خطوات الطلب</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>راجع السلة</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>سيبها فاضية لو مش عايزها</t>
+          <t>نعم / لا — الخطوات الثلاثة (1 2 3) اللي في صفحة حول</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>خطوة 3</t>
+          <t>خطوة 1</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>ابعت الطلب واتساب</t>
+          <t>اختار منتجاتك</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2131,156 +1798,190 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>إظهار وصف صفحة حول القديم</t>
+          <t>خطوة 2</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>راجع السلة</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>النصين القديمين تحت اسم المتجر (وصف صفحة حول 1 والمساحة الحرة). نعم/لا</t>
+          <t>سيبها فاضية لو مش عايزها</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>كروت صفحة حول (قناة العروض / الموقع / التواصل)</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>خطوة 3</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>ابعت الطلب واتساب</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>سيبها فاضية لو مش عايزها</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>عنوان كيو آر قناة العروض</t>
+          <t>إظهار وصف صفحة حول القديم</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>قناة العروض (واتساب)</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>عنوان الكارت</t>
+          <t>النصين القديمين تحت اسم المتجر (وصف صفحة حول 1 والمساحة الحرة). نعم/لا</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>رابط قناة العروض</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>رابط قناة واتساب الخاصة بالمتجر. فاضي = الكارت يختفي من صفحة حول</t>
-        </is>
-      </c>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>كروت صفحة حول (قناة العروض / الموقع / التواصل)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>نص زر قناة العروض</t>
+          <t>عنوان كيو آر قناة العروض</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>الانتقال إلى القناة</t>
+          <t>قناة العروض (واتساب)</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>كتابة الزر</t>
+          <t>عنوان الكارت</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>عنوان كيو آر الموقع</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>موقعنا الإلكتروني</t>
-        </is>
-      </c>
+          <t>رابط قناة العروض</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>عنوان الكارت</t>
+          <t>رابط قناة واتساب الخاصة بالمتجر. فاضي = الكارت يختفي من صفحة حول</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>رابط الموقع</t>
+          <t>نص زر قناة العروض</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>https://truly.market.page</t>
+          <t>الانتقال إلى القناة</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>الرابط اللي بيتشارك</t>
+          <t>كتابة الزر</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>نص زر الموقع</t>
+          <t>عنوان كيو آر الموقع</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>مشاركة الموقع</t>
+          <t>موقعنا الإلكتروني</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>كتابة الزر</t>
+          <t>عنوان الكارت</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>عنوان كيو آر التواصل</t>
+          <t>رابط الموقع</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>تواصل معنا</t>
+          <t>https://truly.market.page</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>عنوان الكارت</t>
+          <t>الرابط اللي بيتشارك</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
+          <t>نص زر الموقع</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>مشاركة الموقع</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>كتابة الزر</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>عنوان كيو آر التواصل</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>تواصل معنا</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>عنوان الكارت</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
           <t>نص زر التواصل</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>مراسلة للإستفسار</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>كتابة الزر</t>
         </is>
@@ -2299,7 +2000,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002B463C"/>
+    <tabColor rgb="005A3114"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2316,37 +2017,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>القسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>الاسم المعروض</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>ظاهر</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>الترتيب</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>اللون</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>أيقونة</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -3004,47 +2705,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>نوع الاستهداف</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>القسم_المستهدف</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>ظاهر</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>الترتيب</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>العنوان</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>العنوان الفرعي</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>نص الزر</t>
         </is>
@@ -3447,42 +3148,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>مكان_البانر</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>نوع الاستهداف</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>القسم أو المنتج المستهدف</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>ظاهر</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>العنوان</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>العنوان الفرعي</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>نص الزر</t>
         </is>
@@ -3774,32 +3475,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>نوع الاستهداف</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>القسم_المستهدف</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>ظاهر</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>الترتيب</t>
         </is>
@@ -4124,7 +3825,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003B86C9"/>
+    <tabColor rgb="00F9B914"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4137,17 +3838,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>رقم_الصفحة</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>ظاهر</t>
         </is>
@@ -4226,7 +3927,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002B463C"/>
+    <tabColor rgb="00DE5718"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4239,17 +3940,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -4585,11 +4286,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0025D366"/>
+    <tabColor rgb="005A3114"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4598,17 +4299,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -4822,84 +4523,68 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>نص بداية رسالة الطلب</t>
+          <t>رسالة نهاية الطلب</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>فاتورة</t>
+          <t>شكراً لاختياركم ترولي ماركت</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>(غير مستخدم حالياً — أول سطر في الرسالة «فاتورة» ثابت)</t>
+          <t>سطر آخر الرسالة (يفضل بدون إيموجي)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>رسالة نهاية الطلب</t>
+          <t>طريقة إرسال الطلب</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>شكراً لاختياركم ترولي ماركت</t>
+          <t>نص فقط</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>سطر آخر الرسالة (يفضل بدون إيموجي)</t>
+          <t>نص فقط (الأسرع: يفتح واتساب المتجر مباشرة والرسالة مرتّبة كفاتورة) / رابط الفاتورة + النص (يرفع صورة الفاتورة ويبعت رابطها، أبطأ) / مشاركة الصورة</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>طريقة إرسال الطلب</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>نص فقط</t>
-        </is>
-      </c>
+          <t>رابط تسجيل الطلبات</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>نص فقط (الأسرع: يفتح واتساب المتجر مباشرة والرسالة مرتّبة كفاتورة) / رابط الفاتورة + النص (يرفع صورة الفاتورة ويبعت رابطها، أبطأ) / مشاركة الصورة</t>
+          <t>رابط Web App من Google Apps Script. سيبه فاضي لو مش مفعّل. اتبع دليل_الربط_جوجل_شيت</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>رابط تسجيل الطلبات</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n"/>
+          <t>تفعيل حساب الزائر</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>رابط Web App من Google Apps Script. سيبه فاضي لو مش مفعّل. اتبع دليل_الربط_جوجل_شيت</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>تفعيل حساب الزائر</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
           <t>نعم = زرار "حسابي" يظهر في الموقع (الزائر يكتب اسمه ورقم موبايله بس)، لا = يختفي</t>
         </is>
       </c>
     </row>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="اختار من القائمة" type="list" errorStyle="warning">
@@ -4922,11 +4607,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E0457B"/>
+    <tabColor rgb="00F9B914"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4935,17 +4620,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الإعداد</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>شرح بسيط</t>
         </is>
@@ -4963,237 +4648,237 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>المظهر الافتراضي</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>فاتح</t>
+          <t>اللون الرئيسي</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>#DE5718</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>الموقع بدون وضع ليلي — الخانة دي ما بتأثرش</t>
+          <t>الأزرار والعناوين</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>اللون الرئيسي</t>
+          <t>اللون الثانوي</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>#DE5718</t>
+          <t>#5A3114</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>الأزرار والعناوين</t>
+          <t>الأزرار الثانوية</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>اللون الثانوي</t>
+          <t>لون الخلفية</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>#5A3114</t>
+          <t>#FCFAF5</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>الأزرار الثانوية</t>
+          <t>خلفية الموقع</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>لون الخلفية</t>
+          <t>لون البطاقات</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>#FCFAF5</t>
+          <t>#F4F1E9</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>خلفية الموقع</t>
+          <t>خلفية الكروت</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>لون البطاقات</t>
+          <t>لون النص</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>#F4F1E9</t>
+          <t>#3B2410</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>خلفية الكروت</t>
+          <t>لون الكتابة</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>لون النص</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>#3B2410</t>
+          <t>تلوين الأقسام بألوانها</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>لون الكتابة</t>
+          <t>نعم = كل قسم بلونه (الأيقونة والشريط السفلي وبطاقات المنتجات). لا = الأخضر للكل. ألوان الأقسام من شيت إدارة الأقسام</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>تلوين الأقسام بألوانها</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>لون عروض اليوم</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>#DE5718</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>نعم = كل قسم بلونه (الأيقونة والشريط السفلي وبطاقات المنتجات). لا = الأخضر للكل. ألوان الأقسام من شيت إدارة الأقسام</t>
+          <t>البرتقالي الثابت: بيظهر في قسم العروض بس (قوس البطاقات وعنوان العروض)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>لون عروض اليوم</t>
+          <t>لون خصم المنتجات</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>#DE5718</t>
+          <t>#F9B914</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>البرتقالي الثابت: بيظهر في قسم العروض بس (قوس البطاقات وعنوان العروض)</t>
+          <t>بادج الخصم — أحمر ساطع هادي (مش غامق)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>لون خصم المنتجات</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>#F9B914</t>
+          <t>هالات الألوان</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>بادج الخصم — أحمر ساطع هادي (مش غامق)</t>
+          <t>نعم / لا — الهالة الملونة حوالين كروت المنتجات ومربعات الأقسام</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>هالات الألوان</t>
+          <t>قوة الهالات</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>متوسطة</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>نعم / لا — الهالة الملونة حوالين كروت المنتجات ومربعات الأقسام</t>
+          <t>خفيفة / متوسطة / قوية — شدة الهالة الملونة (تتأثر بـ «هالات الألوان»)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>قوة الهالات</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
+          <t>لون زر السلة</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>#DE5718</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>خفيفة / متوسطة / قوية — شدة الهالة الملونة (تتأثر بـ «هالات الألوان»)</t>
+          <t>زرار السلة فوق في الشريط العلوي</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>لون زر السلة</t>
+          <t>لون الشريط المتحرك</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>#DE5718</t>
+          <t>#5A3114</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>زرار السلة فوق في الشريط العلوي</t>
+          <t>الشريط اللي بيلف تحت الهيرو</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>لون الشريط المتحرك</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>ألوان الهوية (من كانفا)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>درجة الأخضر الداكن</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>#5A3114</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>الشريط اللي بيلف تحت الهيرو</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>ألوان الهوية (من كانفا)</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>الفوتر والشريط السفلي وهيدر السلة (بني الهوية)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>درجة الأخضر الداكن</t>
+          <t>درجة الأخضر</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -5210,29 +4895,29 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>درجة الأخضر</t>
+          <t>درجة الأخضر الفاتح</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>#5A3114</t>
+          <t>#E6DCC8</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>الفوتر والشريط السفلي وهيدر السلة (بني الهوية)</t>
+          <t>لمسات خفيفة (للاستخدام في الأقسام)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>درجة الأخضر الفاتح</t>
+          <t>درجة الأخضر الأفتح</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>#E6DCC8</t>
+          <t>#F4F1E9</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -5244,46 +4929,46 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>درجة الأخضر الأفتح</t>
+          <t>درجة البرتقالي</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>#F4F1E9</t>
+          <t>#DE5718</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>لمسات خفيفة (للاستخدام في الأقسام)</t>
+          <t>العروض والأسعار والتمييز</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>درجة البرتقالي</t>
+          <t>درجة الأصفر</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>#DE5718</t>
+          <t>#F9B914</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>العروض والأسعار والتمييز</t>
+          <t>لمسات وأقسام</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>درجة الأصفر</t>
+          <t>درجة الأحمر</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>#F9B914</t>
+          <t>#C8381F</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -5295,54 +4980,38 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>درجة الأحمر</t>
+          <t>درجة الكريمي الفاتح</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>#C8381F</t>
+          <t>#FCFAF5</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>لمسات وأقسام</t>
+          <t>خلفيات فاتحة ونص الفوتر</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>درجة الكريمي الفاتح</t>
+          <t>درجة الكريمي</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>#FCFAF5</t>
+          <t>#F4F1E9</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>خلفيات فاتحة ونص الفوتر</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>درجة الكريمي</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>#F4F1E9</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
           <t>خلفية الموقع</t>
         </is>
       </c>
     </row>
+    <row r="25" ht="22" customHeight="1"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="اختار من القائمة" type="list" errorStyle="warning">
